--- a/home/data/Lotte_Material_Inventory.xlsx
+++ b/home/data/Lotte_Material_Inventory.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Settings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/home/data/Lotte_Material_Inventory.xlsx
+++ b/home/data/Lotte_Material_Inventory.xlsx
@@ -21,9 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -54,9 +56,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -24543,7 +24546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24816,6 +24819,49 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B5" t="n">
+        <v>410</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-4822</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24878,7 +24924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE5"/>
+  <dimension ref="A1:DE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26392,6 +26438,227 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>410</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4822</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="1" t="n">
+        <v>46266.98631016162</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>R-ray(se-75)</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>4822</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>122961000</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>Se-75 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>조건없음 (1.0)</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="inlineStr"/>
+      <c r="CG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="inlineStr"/>
+      <c r="CN6" t="inlineStr"/>
+      <c r="CO6" t="inlineStr"/>
+      <c r="CP6" t="inlineStr"/>
+      <c r="CQ6" t="inlineStr"/>
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="inlineStr"/>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr"/>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr"/>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr"/>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>주배관</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr"/>
+      <c r="DC6" t="inlineStr"/>
+      <c r="DD6" t="inlineStr"/>
+      <c r="DE6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/home/data/Lotte_Material_Inventory.xlsx
+++ b/home/data/Lotte_Material_Inventory.xlsx
@@ -21,9 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -54,9 +56,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -24649,7 +24652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W94"/>
+  <dimension ref="A1:W110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30228,6 +30231,758 @@
       <c r="V94" t="inlineStr"/>
       <c r="W94" t="inlineStr"/>
     </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>45992.69273418081</v>
+      </c>
+      <c r="B95" t="n">
+        <v>420</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>45992.69273418081</v>
+      </c>
+      <c r="B96" t="n">
+        <v>418</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B97" t="n">
+        <v>410</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>-100</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>주임 이은수, 대리 우명광, 주임 김진환, 주임 김진환</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B98" t="n">
+        <v>410</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>-55</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>주임 이은수, 대리 우명광, 주임 김진환, 주임 김진환</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>45993.69565744384</v>
+      </c>
+      <c r="B99" t="n">
+        <v>420</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>부장 주진철, 부장 이봉주</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>45999.69990378177</v>
+      </c>
+      <c r="B100" t="n">
+        <v>420</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>부장 주진철, 부장 이봉주</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B101" t="n">
+        <v>410</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>-50</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>주임 이경재, 대리 우명광, 주임 김진환, 주임 김성렬, 부장 주진철</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B102" t="n">
+        <v>410</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>-50</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>주임 이은수, 대리 우명광, 주임 김진환, 주임 김성렬, 부장 주진철</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B103" t="n">
+        <v>410</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>-70</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>주임 이은수, 대리 우명광, 주임 김진환, 주임 김성렬</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B104" t="n">
+        <v>410</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>-40</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>주임 이은수, 대리 우명광, 주임 김진환, 주임 김성렬, 부장 주진철</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B105" t="n">
+        <v>410</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>-47</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>주임 이경재, 대리 우명광, 주임 김진환, 주임 김성렬, 부장 주진철</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
+      <c r="W105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B106" t="n">
+        <v>410</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>-53</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>주임 이경재, 대리 우명광, 주임 김진환, 주임 김성렬, 부장 주진철</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
+      <c r="W106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B107" t="n">
+        <v>410</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>-39</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>주임 이경재, 대리 우명광, 주임 김진환, 주임 김성렬, 부장 주진철, 주임 이경재</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46002.70486741902</v>
+      </c>
+      <c r="B108" t="n">
+        <v>420</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
+      <c r="W108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>46002.70486741902</v>
+      </c>
+      <c r="B109" t="n">
+        <v>418</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B110" t="n">
+        <v>410</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>-48</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>K1 PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>과장 주영광, 대리 우명광, 주임 김진환, 주임 김성렬, 주임 이경재</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30290,7 +31045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE111"/>
+  <dimension ref="A1:DE125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60138,6 +60893,3836 @@
         <v>0</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="n">
+        <v>80</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" s="1" t="n">
+        <v>46270.6927341525</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>4200</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>336000</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~22:00</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr"/>
+      <c r="AA112" t="inlineStr"/>
+      <c r="AB112" t="inlineStr"/>
+      <c r="AC112" t="inlineStr"/>
+      <c r="AD112" t="inlineStr"/>
+      <c r="AE112" t="inlineStr"/>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="inlineStr"/>
+      <c r="AH112" t="inlineStr"/>
+      <c r="AI112" t="inlineStr"/>
+      <c r="AJ112" t="inlineStr"/>
+      <c r="AK112" t="inlineStr"/>
+      <c r="AL112" t="inlineStr"/>
+      <c r="AM112" t="inlineStr"/>
+      <c r="AN112" t="inlineStr"/>
+      <c r="AO112" t="inlineStr"/>
+      <c r="AP112" t="inlineStr"/>
+      <c r="AQ112" t="inlineStr"/>
+      <c r="AR112" t="inlineStr"/>
+      <c r="AS112" t="inlineStr"/>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AU112" t="inlineStr"/>
+      <c r="AV112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr"/>
+      <c r="AX112" t="inlineStr"/>
+      <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG112" t="inlineStr">
+        <is>
+          <t>95가0200 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="BH112" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BI112" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:안함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:안함</t>
+        </is>
+      </c>
+      <c r="BJ112" t="inlineStr"/>
+      <c r="BK112" t="inlineStr"/>
+      <c r="BL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM112" t="inlineStr"/>
+      <c r="BN112" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO112" t="inlineStr"/>
+      <c r="BP112" t="inlineStr"/>
+      <c r="BQ112" t="inlineStr"/>
+      <c r="BR112" t="inlineStr"/>
+      <c r="BS112" t="inlineStr"/>
+      <c r="BT112" t="inlineStr"/>
+      <c r="BU112" t="inlineStr"/>
+      <c r="BV112" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="BW112" t="inlineStr"/>
+      <c r="BX112" t="inlineStr"/>
+      <c r="BY112" t="inlineStr"/>
+      <c r="BZ112" t="inlineStr">
+        <is>
+          <t>I/D</t>
+        </is>
+      </c>
+      <c r="CA112" t="inlineStr"/>
+      <c r="CB112" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC112" t="inlineStr">
+        <is>
+          <t>250mm 초과 [10인치 이상] (1.0)</t>
+        </is>
+      </c>
+      <c r="CD112" t="inlineStr"/>
+      <c r="CE112" t="inlineStr"/>
+      <c r="CF112" t="inlineStr"/>
+      <c r="CG112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM112" t="inlineStr"/>
+      <c r="CN112" t="inlineStr"/>
+      <c r="CO112" t="inlineStr"/>
+      <c r="CP112" t="inlineStr"/>
+      <c r="CQ112" t="inlineStr"/>
+      <c r="CR112" t="inlineStr"/>
+      <c r="CS112" t="inlineStr"/>
+      <c r="CT112" t="inlineStr"/>
+      <c r="CU112" t="inlineStr"/>
+      <c r="CV112" t="inlineStr"/>
+      <c r="CW112" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX112" t="inlineStr"/>
+      <c r="CY112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ112" t="inlineStr"/>
+      <c r="DA112" t="inlineStr">
+        <is>
+          <t>주배관</t>
+        </is>
+      </c>
+      <c r="DB112" t="inlineStr"/>
+      <c r="DC112" t="inlineStr"/>
+      <c r="DD112" t="inlineStr"/>
+      <c r="DE112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>410</v>
+      </c>
+      <c r="D113" t="n">
+        <v>100</v>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" s="1" t="n">
+        <v>46270.69409599712</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>주임 이은수</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>R-ray(se-75)</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>대리 우명광</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>주임 김진환</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>주임 김진환</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr"/>
+      <c r="AH113" t="inlineStr"/>
+      <c r="AI113" t="inlineStr"/>
+      <c r="AJ113" t="inlineStr"/>
+      <c r="AK113" t="inlineStr"/>
+      <c r="AL113" t="inlineStr"/>
+      <c r="AM113" t="inlineStr"/>
+      <c r="AN113" t="inlineStr"/>
+      <c r="AO113" t="inlineStr"/>
+      <c r="AP113" t="inlineStr"/>
+      <c r="AQ113" t="inlineStr"/>
+      <c r="AR113" t="inlineStr"/>
+      <c r="AS113" t="inlineStr"/>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AU113" t="inlineStr"/>
+      <c r="AV113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr"/>
+      <c r="AX113" t="inlineStr"/>
+      <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG113" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="BH113" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BI113" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ113" t="inlineStr"/>
+      <c r="BK113" t="inlineStr"/>
+      <c r="BL113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM113" t="inlineStr"/>
+      <c r="BN113" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO113" t="inlineStr"/>
+      <c r="BP113" t="inlineStr"/>
+      <c r="BQ113" t="inlineStr"/>
+      <c r="BR113" t="inlineStr"/>
+      <c r="BS113" t="inlineStr"/>
+      <c r="BT113" t="inlineStr"/>
+      <c r="BU113" t="inlineStr"/>
+      <c r="BV113" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="BW113" t="inlineStr"/>
+      <c r="BX113" t="inlineStr"/>
+      <c r="BY113" t="inlineStr"/>
+      <c r="BZ113" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA113" t="inlineStr"/>
+      <c r="CB113" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC113" t="inlineStr">
+        <is>
+          <t>Se-75 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD113" t="inlineStr">
+        <is>
+          <t>조건없음 (1.0)</t>
+        </is>
+      </c>
+      <c r="CE113" t="inlineStr"/>
+      <c r="CF113" t="inlineStr"/>
+      <c r="CG113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM113" t="inlineStr"/>
+      <c r="CN113" t="inlineStr"/>
+      <c r="CO113" t="inlineStr"/>
+      <c r="CP113" t="inlineStr"/>
+      <c r="CQ113" t="inlineStr"/>
+      <c r="CR113" t="inlineStr"/>
+      <c r="CS113" t="inlineStr"/>
+      <c r="CT113" t="inlineStr"/>
+      <c r="CU113" t="inlineStr"/>
+      <c r="CV113" t="inlineStr"/>
+      <c r="CW113" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX113" t="inlineStr"/>
+      <c r="CY113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ113" t="inlineStr"/>
+      <c r="DA113" t="inlineStr">
+        <is>
+          <t>주배관</t>
+        </is>
+      </c>
+      <c r="DB113" t="inlineStr"/>
+      <c r="DC113" t="inlineStr"/>
+      <c r="DD113" t="inlineStr"/>
+      <c r="DE113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>410</v>
+      </c>
+      <c r="D114" t="n">
+        <v>55</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" s="1" t="n">
+        <v>46270.69484850537</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>주임 이은수</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>R-ray(se-75)</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" t="n">
+        <v>1402500</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V114" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>대리 우명광</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>주임 김진환</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>주임 김진환</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr"/>
+      <c r="AH114" t="inlineStr"/>
+      <c r="AI114" t="inlineStr"/>
+      <c r="AJ114" t="inlineStr"/>
+      <c r="AK114" t="inlineStr"/>
+      <c r="AL114" t="inlineStr"/>
+      <c r="AM114" t="inlineStr"/>
+      <c r="AN114" t="inlineStr"/>
+      <c r="AO114" t="inlineStr"/>
+      <c r="AP114" t="inlineStr"/>
+      <c r="AQ114" t="inlineStr"/>
+      <c r="AR114" t="inlineStr"/>
+      <c r="AS114" t="inlineStr"/>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AU114" t="inlineStr"/>
+      <c r="AV114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr"/>
+      <c r="AX114" t="inlineStr"/>
+      <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG114" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="BH114" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BI114" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ114" t="inlineStr"/>
+      <c r="BK114" t="inlineStr"/>
+      <c r="BL114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM114" t="inlineStr"/>
+      <c r="BN114" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO114" t="inlineStr"/>
+      <c r="BP114" t="inlineStr"/>
+      <c r="BQ114" t="inlineStr"/>
+      <c r="BR114" t="inlineStr"/>
+      <c r="BS114" t="inlineStr"/>
+      <c r="BT114" t="inlineStr"/>
+      <c r="BU114" t="inlineStr"/>
+      <c r="BV114" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="BW114" t="inlineStr"/>
+      <c r="BX114" t="inlineStr"/>
+      <c r="BY114" t="inlineStr"/>
+      <c r="BZ114" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA114" t="inlineStr"/>
+      <c r="CB114" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC114" t="inlineStr">
+        <is>
+          <t>Se-75 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD114" t="inlineStr">
+        <is>
+          <t>조건없음 (1.0)</t>
+        </is>
+      </c>
+      <c r="CE114" t="inlineStr"/>
+      <c r="CF114" t="inlineStr"/>
+      <c r="CG114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM114" t="inlineStr"/>
+      <c r="CN114" t="inlineStr"/>
+      <c r="CO114" t="inlineStr"/>
+      <c r="CP114" t="inlineStr"/>
+      <c r="CQ114" t="inlineStr"/>
+      <c r="CR114" t="inlineStr"/>
+      <c r="CS114" t="inlineStr"/>
+      <c r="CT114" t="inlineStr"/>
+      <c r="CU114" t="inlineStr"/>
+      <c r="CV114" t="inlineStr"/>
+      <c r="CW114" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX114" t="inlineStr"/>
+      <c r="CY114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ114" t="inlineStr"/>
+      <c r="DA114" t="inlineStr">
+        <is>
+          <t>주배관</t>
+        </is>
+      </c>
+      <c r="DB114" t="inlineStr"/>
+      <c r="DC114" t="inlineStr"/>
+      <c r="DD114" t="inlineStr"/>
+      <c r="DE114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="n">
+        <v>30</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" s="1" t="n">
+        <v>46270.6956574165</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>4200</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>126000</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~18:00</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr"/>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>부장 이봉주</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr"/>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
+      <c r="AC115" t="inlineStr"/>
+      <c r="AD115" t="inlineStr"/>
+      <c r="AE115" t="inlineStr"/>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="inlineStr"/>
+      <c r="AH115" t="inlineStr"/>
+      <c r="AI115" t="inlineStr"/>
+      <c r="AJ115" t="inlineStr"/>
+      <c r="AK115" t="inlineStr"/>
+      <c r="AL115" t="inlineStr"/>
+      <c r="AM115" t="inlineStr"/>
+      <c r="AN115" t="inlineStr"/>
+      <c r="AO115" t="inlineStr"/>
+      <c r="AP115" t="inlineStr"/>
+      <c r="AQ115" t="inlineStr"/>
+      <c r="AR115" t="inlineStr"/>
+      <c r="AS115" t="inlineStr"/>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AU115" t="inlineStr"/>
+      <c r="AV115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr"/>
+      <c r="AX115" t="inlineStr"/>
+      <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG115" t="inlineStr">
+        <is>
+          <t>81루5100 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="BH115" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BI115" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:안함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:안함</t>
+        </is>
+      </c>
+      <c r="BJ115" t="inlineStr"/>
+      <c r="BK115" t="inlineStr"/>
+      <c r="BL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM115" t="inlineStr"/>
+      <c r="BN115" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO115" t="inlineStr"/>
+      <c r="BP115" t="inlineStr"/>
+      <c r="BQ115" t="inlineStr"/>
+      <c r="BR115" t="inlineStr"/>
+      <c r="BS115" t="inlineStr"/>
+      <c r="BT115" t="inlineStr"/>
+      <c r="BU115" t="inlineStr"/>
+      <c r="BV115" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="BW115" t="inlineStr"/>
+      <c r="BX115" t="inlineStr"/>
+      <c r="BY115" t="inlineStr"/>
+      <c r="BZ115" t="inlineStr">
+        <is>
+          <t>I/D</t>
+        </is>
+      </c>
+      <c r="CA115" t="inlineStr"/>
+      <c r="CB115" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC115" t="inlineStr">
+        <is>
+          <t>250mm 초과 [10인치 이상] (1.0)</t>
+        </is>
+      </c>
+      <c r="CD115" t="inlineStr"/>
+      <c r="CE115" t="inlineStr"/>
+      <c r="CF115" t="inlineStr"/>
+      <c r="CG115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM115" t="inlineStr"/>
+      <c r="CN115" t="inlineStr"/>
+      <c r="CO115" t="inlineStr"/>
+      <c r="CP115" t="inlineStr"/>
+      <c r="CQ115" t="inlineStr"/>
+      <c r="CR115" t="inlineStr"/>
+      <c r="CS115" t="inlineStr"/>
+      <c r="CT115" t="inlineStr"/>
+      <c r="CU115" t="inlineStr"/>
+      <c r="CV115" t="inlineStr"/>
+      <c r="CW115" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX115" t="inlineStr"/>
+      <c r="CY115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ115" t="inlineStr"/>
+      <c r="DA115" t="inlineStr">
+        <is>
+          <t>주배관</t>
+        </is>
+      </c>
+      <c r="DB115" t="inlineStr"/>
+      <c r="DC115" t="inlineStr"/>
+      <c r="DD115" t="inlineStr"/>
+      <c r="DE115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="n">
+        <v>204</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" s="1" t="n">
+        <v>46270.69990375041</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="n">
+        <v>204</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>4200</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>856800</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="V116" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~18:00</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr"/>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>부장 이봉주</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr"/>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr"/>
+      <c r="AC116" t="inlineStr"/>
+      <c r="AD116" t="inlineStr"/>
+      <c r="AE116" t="inlineStr"/>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="inlineStr"/>
+      <c r="AH116" t="inlineStr"/>
+      <c r="AI116" t="inlineStr"/>
+      <c r="AJ116" t="inlineStr"/>
+      <c r="AK116" t="inlineStr"/>
+      <c r="AL116" t="inlineStr"/>
+      <c r="AM116" t="inlineStr"/>
+      <c r="AN116" t="inlineStr"/>
+      <c r="AO116" t="inlineStr"/>
+      <c r="AP116" t="inlineStr"/>
+      <c r="AQ116" t="inlineStr"/>
+      <c r="AR116" t="inlineStr"/>
+      <c r="AS116" t="inlineStr"/>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AU116" t="inlineStr"/>
+      <c r="AV116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr"/>
+      <c r="AX116" t="inlineStr"/>
+      <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG116" t="inlineStr">
+        <is>
+          <t>81루5100 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="BH116" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BI116" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:안함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:안함</t>
+        </is>
+      </c>
+      <c r="BJ116" t="inlineStr"/>
+      <c r="BK116" t="inlineStr"/>
+      <c r="BL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM116" t="inlineStr"/>
+      <c r="BN116" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO116" t="inlineStr"/>
+      <c r="BP116" t="inlineStr"/>
+      <c r="BQ116" t="inlineStr"/>
+      <c r="BR116" t="inlineStr"/>
+      <c r="BS116" t="inlineStr"/>
+      <c r="BT116" t="inlineStr"/>
+      <c r="BU116" t="inlineStr"/>
+      <c r="BV116" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="BW116" t="inlineStr"/>
+      <c r="BX116" t="inlineStr"/>
+      <c r="BY116" t="inlineStr"/>
+      <c r="BZ116" t="inlineStr">
+        <is>
+          <t>I/D</t>
+        </is>
+      </c>
+      <c r="CA116" t="inlineStr"/>
+      <c r="CB116" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC116" t="inlineStr">
+        <is>
+          <t>250mm 초과 [10인치 이상] (1.0)</t>
+        </is>
+      </c>
+      <c r="CD116" t="inlineStr"/>
+      <c r="CE116" t="inlineStr"/>
+      <c r="CF116" t="inlineStr"/>
+      <c r="CG116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM116" t="inlineStr"/>
+      <c r="CN116" t="inlineStr"/>
+      <c r="CO116" t="inlineStr"/>
+      <c r="CP116" t="inlineStr"/>
+      <c r="CQ116" t="inlineStr"/>
+      <c r="CR116" t="inlineStr"/>
+      <c r="CS116" t="inlineStr"/>
+      <c r="CT116" t="inlineStr"/>
+      <c r="CU116" t="inlineStr"/>
+      <c r="CV116" t="inlineStr"/>
+      <c r="CW116" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX116" t="inlineStr"/>
+      <c r="CY116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ116" t="inlineStr"/>
+      <c r="DA116" t="inlineStr">
+        <is>
+          <t>주배관</t>
+        </is>
+      </c>
+      <c r="DB116" t="inlineStr"/>
+      <c r="DC116" t="inlineStr"/>
+      <c r="DD116" t="inlineStr"/>
+      <c r="DE116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>410</v>
+      </c>
+      <c r="D117" t="n">
+        <v>50</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" s="1" t="n">
+        <v>46270.70089576427</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>주임 이경재</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>R-ray(se-75)</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V117" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>대리 우명광</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>주임 김진환</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>주임 김성렬</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr"/>
+      <c r="AL117" t="inlineStr"/>
+      <c r="AM117" t="inlineStr"/>
+      <c r="AN117" t="inlineStr"/>
+      <c r="AO117" t="inlineStr"/>
+      <c r="AP117" t="inlineStr"/>
+      <c r="AQ117" t="inlineStr"/>
+      <c r="AR117" t="inlineStr"/>
+      <c r="AS117" t="inlineStr"/>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AU117" t="inlineStr"/>
+      <c r="AV117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr"/>
+      <c r="AX117" t="inlineStr"/>
+      <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG117" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="BH117" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BI117" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ117" t="inlineStr"/>
+      <c r="BK117" t="inlineStr"/>
+      <c r="BL117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM117" t="inlineStr"/>
+      <c r="BN117" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO117" t="inlineStr"/>
+      <c r="BP117" t="inlineStr"/>
+      <c r="BQ117" t="inlineStr"/>
+      <c r="BR117" t="inlineStr"/>
+      <c r="BS117" t="inlineStr"/>
+      <c r="BT117" t="inlineStr"/>
+      <c r="BU117" t="inlineStr"/>
+      <c r="BV117" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="BW117" t="inlineStr"/>
+      <c r="BX117" t="inlineStr"/>
+      <c r="BY117" t="inlineStr"/>
+      <c r="BZ117" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA117" t="inlineStr"/>
+      <c r="CB117" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC117" t="inlineStr">
+        <is>
+          <t>Se-75 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD117" t="inlineStr">
+        <is>
+          <t>조건없음 (1.0)</t>
+        </is>
+      </c>
+      <c r="CE117" t="inlineStr"/>
+      <c r="CF117" t="inlineStr"/>
+      <c r="CG117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM117" t="inlineStr"/>
+      <c r="CN117" t="inlineStr"/>
+      <c r="CO117" t="inlineStr"/>
+      <c r="CP117" t="inlineStr"/>
+      <c r="CQ117" t="inlineStr"/>
+      <c r="CR117" t="inlineStr"/>
+      <c r="CS117" t="inlineStr"/>
+      <c r="CT117" t="inlineStr"/>
+      <c r="CU117" t="inlineStr"/>
+      <c r="CV117" t="inlineStr"/>
+      <c r="CW117" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX117" t="inlineStr"/>
+      <c r="CY117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ117" t="inlineStr"/>
+      <c r="DA117" t="inlineStr">
+        <is>
+          <t>주배관</t>
+        </is>
+      </c>
+      <c r="DB117" t="inlineStr"/>
+      <c r="DC117" t="inlineStr"/>
+      <c r="DD117" t="inlineStr"/>
+      <c r="DE117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>410</v>
+      </c>
+      <c r="D118" t="n">
+        <v>50</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" s="1" t="n">
+        <v>46270.70108447342</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>주임 이은수</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>R-ray(se-75)</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V118" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>55,000</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>대리 우명광</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>55,000</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>주임 김진환</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>55,000</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>주임 김성렬</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr"/>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>55,000</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr"/>
+      <c r="AL118" t="inlineStr"/>
+      <c r="AM118" t="inlineStr"/>
+      <c r="AN118" t="inlineStr"/>
+      <c r="AO118" t="inlineStr"/>
+      <c r="AP118" t="inlineStr"/>
+      <c r="AQ118" t="inlineStr"/>
+      <c r="AR118" t="inlineStr"/>
+      <c r="AS118" t="inlineStr"/>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AU118" t="inlineStr"/>
+      <c r="AV118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr"/>
+      <c r="AX118" t="inlineStr"/>
+      <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG118" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="BH118" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BI118" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ118" t="inlineStr"/>
+      <c r="BK118" t="inlineStr"/>
+      <c r="BL118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM118" t="inlineStr"/>
+      <c r="BN118" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO118" t="inlineStr"/>
+      <c r="BP118" t="inlineStr"/>
+      <c r="BQ118" t="inlineStr"/>
+      <c r="BR118" t="inlineStr"/>
+      <c r="BS118" t="inlineStr"/>
+      <c r="BT118" t="inlineStr"/>
+      <c r="BU118" t="inlineStr"/>
+      <c r="BV118" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="BW118" t="inlineStr"/>
+      <c r="BX118" t="inlineStr"/>
+      <c r="BY118" t="inlineStr"/>
+      <c r="BZ118" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA118" t="inlineStr"/>
+      <c r="CB118" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC118" t="inlineStr">
+        <is>
+          <t>Se-75 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD118" t="inlineStr">
+        <is>
+          <t>조건없음 (1.0)</t>
+        </is>
+      </c>
+      <c r="CE118" t="inlineStr"/>
+      <c r="CF118" t="inlineStr"/>
+      <c r="CG118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM118" t="inlineStr"/>
+      <c r="CN118" t="inlineStr"/>
+      <c r="CO118" t="inlineStr"/>
+      <c r="CP118" t="inlineStr"/>
+      <c r="CQ118" t="inlineStr"/>
+      <c r="CR118" t="inlineStr"/>
+      <c r="CS118" t="inlineStr"/>
+      <c r="CT118" t="inlineStr"/>
+      <c r="CU118" t="inlineStr"/>
+      <c r="CV118" t="inlineStr"/>
+      <c r="CW118" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX118" t="inlineStr"/>
+      <c r="CY118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ118" t="inlineStr"/>
+      <c r="DA118" t="inlineStr">
+        <is>
+          <t>주배관</t>
+        </is>
+      </c>
+      <c r="DB118" t="inlineStr"/>
+      <c r="DC118" t="inlineStr"/>
+      <c r="DD118" t="inlineStr"/>
+      <c r="DE118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>410</v>
+      </c>
+      <c r="D119" t="n">
+        <v>70</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" s="1" t="n">
+        <v>46270.70124387546</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>주임 이은수</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>R-ray(se-75)</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>1785000</v>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V119" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>대리 우명광</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>주임 김진환</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>주임 김성렬</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr"/>
+      <c r="AH119" t="inlineStr"/>
+      <c r="AI119" t="inlineStr"/>
+      <c r="AJ119" t="inlineStr"/>
+      <c r="AK119" t="inlineStr"/>
+      <c r="AL119" t="inlineStr"/>
+      <c r="AM119" t="inlineStr"/>
+      <c r="AN119" t="inlineStr"/>
+      <c r="AO119" t="inlineStr"/>
+      <c r="AP119" t="inlineStr"/>
+      <c r="AQ119" t="inlineStr"/>
+      <c r="AR119" t="inlineStr"/>
+      <c r="AS119" t="inlineStr"/>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AU119" t="inlineStr"/>
+      <c r="AV119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr"/>
+      <c r="AX119" t="inlineStr"/>
+      <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG119" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="BH119" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BI119" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ119" t="inlineStr"/>
+      <c r="BK119" t="inlineStr"/>
+      <c r="BL119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM119" t="inlineStr"/>
+      <c r="BN119" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO119" t="inlineStr"/>
+      <c r="BP119" t="inlineStr"/>
+      <c r="BQ119" t="inlineStr"/>
+      <c r="BR119" t="inlineStr"/>
+      <c r="BS119" t="inlineStr"/>
+      <c r="BT119" t="inlineStr"/>
+      <c r="BU119" t="inlineStr"/>
+      <c r="BV119" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="BW119" t="inlineStr"/>
+      <c r="BX119" t="inlineStr"/>
+      <c r="BY119" t="inlineStr"/>
+      <c r="BZ119" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA119" t="inlineStr"/>
+      <c r="CB119" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC119" t="inlineStr">
+        <is>
+          <t>Se-75 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD119" t="inlineStr">
+        <is>
+          <t>조건없음 (1.0)</t>
+        </is>
+      </c>
+      <c r="CE119" t="inlineStr"/>
+      <c r="CF119" t="inlineStr"/>
+      <c r="CG119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM119" t="inlineStr"/>
+      <c r="CN119" t="inlineStr"/>
+      <c r="CO119" t="inlineStr"/>
+      <c r="CP119" t="inlineStr"/>
+      <c r="CQ119" t="inlineStr"/>
+      <c r="CR119" t="inlineStr"/>
+      <c r="CS119" t="inlineStr"/>
+      <c r="CT119" t="inlineStr"/>
+      <c r="CU119" t="inlineStr"/>
+      <c r="CV119" t="inlineStr"/>
+      <c r="CW119" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX119" t="inlineStr"/>
+      <c r="CY119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ119" t="inlineStr"/>
+      <c r="DA119" t="inlineStr">
+        <is>
+          <t>주배관</t>
+        </is>
+      </c>
+      <c r="DB119" t="inlineStr"/>
+      <c r="DC119" t="inlineStr"/>
+      <c r="DD119" t="inlineStr"/>
+      <c r="DE119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>410</v>
+      </c>
+      <c r="D120" t="n">
+        <v>40</v>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" s="1" t="n">
+        <v>46270.7014567442</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>주임 이은수</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>R-ray(se-75)</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>1020000</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V120" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>대리 우명광</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>주임 김진환</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>주임 김성렬</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr"/>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~22:00</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr"/>
+      <c r="AL120" t="inlineStr"/>
+      <c r="AM120" t="inlineStr"/>
+      <c r="AN120" t="inlineStr"/>
+      <c r="AO120" t="inlineStr"/>
+      <c r="AP120" t="inlineStr"/>
+      <c r="AQ120" t="inlineStr"/>
+      <c r="AR120" t="inlineStr"/>
+      <c r="AS120" t="inlineStr"/>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AU120" t="inlineStr"/>
+      <c r="AV120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr"/>
+      <c r="AX120" t="inlineStr"/>
+      <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG120" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="BH120" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BI120" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ120" t="inlineStr"/>
+      <c r="BK120" t="inlineStr"/>
+      <c r="BL120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM120" t="inlineStr"/>
+      <c r="BN120" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO120" t="inlineStr"/>
+      <c r="BP120" t="inlineStr"/>
+      <c r="BQ120" t="inlineStr"/>
+      <c r="BR120" t="inlineStr"/>
+      <c r="BS120" t="inlineStr"/>
+      <c r="BT120" t="inlineStr"/>
+      <c r="BU120" t="inlineStr"/>
+      <c r="BV120" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="BW120" t="inlineStr"/>
+      <c r="BX120" t="inlineStr"/>
+      <c r="BY120" t="inlineStr"/>
+      <c r="BZ120" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA120" t="inlineStr"/>
+      <c r="CB120" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC120" t="inlineStr">
+        <is>
+          <t>Se-75 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD120" t="inlineStr">
+        <is>
+          <t>조건없음 (1.0)</t>
+        </is>
+      </c>
+      <c r="CE120" t="inlineStr"/>
+      <c r="CF120" t="inlineStr"/>
+      <c r="CG120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM120" t="inlineStr"/>
+      <c r="CN120" t="inlineStr"/>
+      <c r="CO120" t="inlineStr"/>
+      <c r="CP120" t="inlineStr"/>
+      <c r="CQ120" t="inlineStr"/>
+      <c r="CR120" t="inlineStr"/>
+      <c r="CS120" t="inlineStr"/>
+      <c r="CT120" t="inlineStr"/>
+      <c r="CU120" t="inlineStr"/>
+      <c r="CV120" t="inlineStr"/>
+      <c r="CW120" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX120" t="inlineStr"/>
+      <c r="CY120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ120" t="inlineStr"/>
+      <c r="DA120" t="inlineStr">
+        <is>
+          <t>주배관</t>
+        </is>
+      </c>
+      <c r="DB120" t="inlineStr"/>
+      <c r="DC120" t="inlineStr"/>
+      <c r="DD120" t="inlineStr"/>
+      <c r="DE120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>410</v>
+      </c>
+      <c r="D121" t="n">
+        <v>47</v>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" s="1" t="n">
+        <v>46270.70231902078</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>주임 이경재</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>R-ray(se-75)</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>1198500</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>대리 우명광</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>주임 김진환</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>주임 김성렬</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr"/>
+      <c r="AL121" t="inlineStr"/>
+      <c r="AM121" t="inlineStr"/>
+      <c r="AN121" t="inlineStr"/>
+      <c r="AO121" t="inlineStr"/>
+      <c r="AP121" t="inlineStr"/>
+      <c r="AQ121" t="inlineStr"/>
+      <c r="AR121" t="inlineStr"/>
+      <c r="AS121" t="inlineStr"/>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AU121" t="inlineStr"/>
+      <c r="AV121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr"/>
+      <c r="AX121" t="inlineStr"/>
+      <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG121" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="BH121" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BI121" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ121" t="inlineStr"/>
+      <c r="BK121" t="inlineStr"/>
+      <c r="BL121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM121" t="inlineStr"/>
+      <c r="BN121" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO121" t="inlineStr"/>
+      <c r="BP121" t="inlineStr"/>
+      <c r="BQ121" t="inlineStr"/>
+      <c r="BR121" t="inlineStr"/>
+      <c r="BS121" t="inlineStr"/>
+      <c r="BT121" t="inlineStr"/>
+      <c r="BU121" t="inlineStr"/>
+      <c r="BV121" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="BW121" t="inlineStr"/>
+      <c r="BX121" t="inlineStr"/>
+      <c r="BY121" t="inlineStr"/>
+      <c r="BZ121" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA121" t="inlineStr"/>
+      <c r="CB121" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC121" t="inlineStr">
+        <is>
+          <t>Se-75 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD121" t="inlineStr">
+        <is>
+          <t>조건없음 (1.0)</t>
+        </is>
+      </c>
+      <c r="CE121" t="inlineStr"/>
+      <c r="CF121" t="inlineStr"/>
+      <c r="CG121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM121" t="inlineStr"/>
+      <c r="CN121" t="inlineStr"/>
+      <c r="CO121" t="inlineStr"/>
+      <c r="CP121" t="inlineStr"/>
+      <c r="CQ121" t="inlineStr"/>
+      <c r="CR121" t="inlineStr"/>
+      <c r="CS121" t="inlineStr"/>
+      <c r="CT121" t="inlineStr"/>
+      <c r="CU121" t="inlineStr"/>
+      <c r="CV121" t="inlineStr"/>
+      <c r="CW121" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX121" t="inlineStr"/>
+      <c r="CY121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ121" t="inlineStr"/>
+      <c r="DA121" t="inlineStr">
+        <is>
+          <t>주배관</t>
+        </is>
+      </c>
+      <c r="DB121" t="inlineStr"/>
+      <c r="DC121" t="inlineStr"/>
+      <c r="DD121" t="inlineStr"/>
+      <c r="DE121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>410</v>
+      </c>
+      <c r="D122" t="n">
+        <v>53</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" s="1" t="n">
+        <v>46270.7032602737</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>주임 이경재</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>R-ray(se-75)</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>1351500</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V122" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>대리 우명광</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>주임 김진환</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>주임 김성렬</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>(주야간) 09:00~23:00</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>21,000</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr"/>
+      <c r="AL122" t="inlineStr"/>
+      <c r="AM122" t="inlineStr"/>
+      <c r="AN122" t="inlineStr"/>
+      <c r="AO122" t="inlineStr"/>
+      <c r="AP122" t="inlineStr"/>
+      <c r="AQ122" t="inlineStr"/>
+      <c r="AR122" t="inlineStr"/>
+      <c r="AS122" t="inlineStr"/>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AU122" t="inlineStr"/>
+      <c r="AV122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr"/>
+      <c r="AX122" t="inlineStr"/>
+      <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG122" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스) || 90너4889 (탑차)</t>
+        </is>
+      </c>
+      <c r="BH122" t="inlineStr">
+        <is>
+          <t>40 || 40</t>
+        </is>
+      </c>
+      <c r="BI122" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금 || out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:안함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:안함</t>
+        </is>
+      </c>
+      <c r="BJ122" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> || </t>
+        </is>
+      </c>
+      <c r="BK122" t="inlineStr"/>
+      <c r="BL122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM122" t="inlineStr"/>
+      <c r="BN122" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO122" t="inlineStr"/>
+      <c r="BP122" t="inlineStr"/>
+      <c r="BQ122" t="inlineStr"/>
+      <c r="BR122" t="inlineStr"/>
+      <c r="BS122" t="inlineStr"/>
+      <c r="BT122" t="inlineStr"/>
+      <c r="BU122" t="inlineStr"/>
+      <c r="BV122" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="BW122" t="inlineStr"/>
+      <c r="BX122" t="inlineStr"/>
+      <c r="BY122" t="inlineStr"/>
+      <c r="BZ122" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA122" t="inlineStr"/>
+      <c r="CB122" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC122" t="inlineStr">
+        <is>
+          <t>Se-75 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD122" t="inlineStr">
+        <is>
+          <t>조건없음 (1.0)</t>
+        </is>
+      </c>
+      <c r="CE122" t="inlineStr"/>
+      <c r="CF122" t="inlineStr"/>
+      <c r="CG122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM122" t="inlineStr"/>
+      <c r="CN122" t="inlineStr"/>
+      <c r="CO122" t="inlineStr"/>
+      <c r="CP122" t="inlineStr"/>
+      <c r="CQ122" t="inlineStr"/>
+      <c r="CR122" t="inlineStr"/>
+      <c r="CS122" t="inlineStr"/>
+      <c r="CT122" t="inlineStr"/>
+      <c r="CU122" t="inlineStr"/>
+      <c r="CV122" t="inlineStr"/>
+      <c r="CW122" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX122" t="inlineStr"/>
+      <c r="CY122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ122" t="inlineStr"/>
+      <c r="DA122" t="inlineStr">
+        <is>
+          <t>주배관</t>
+        </is>
+      </c>
+      <c r="DB122" t="inlineStr"/>
+      <c r="DC122" t="inlineStr"/>
+      <c r="DD122" t="inlineStr"/>
+      <c r="DE122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>410</v>
+      </c>
+      <c r="D123" t="n">
+        <v>39</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" s="1" t="n">
+        <v>46270.70438769966</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>주임 이경재</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>R-ray(se-75)</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>994500</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>대리 우명광</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>주임 김진환</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>주임 김성렬</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>주임 이경재</t>
+        </is>
+      </c>
+      <c r="AL123" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr"/>
+      <c r="AN123" t="inlineStr"/>
+      <c r="AO123" t="inlineStr"/>
+      <c r="AP123" t="inlineStr"/>
+      <c r="AQ123" t="inlineStr"/>
+      <c r="AR123" t="inlineStr"/>
+      <c r="AS123" t="inlineStr"/>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AU123" t="inlineStr"/>
+      <c r="AV123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr"/>
+      <c r="AX123" t="inlineStr"/>
+      <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG123" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스) || 90너4889 (탑차)</t>
+        </is>
+      </c>
+      <c r="BH123" t="inlineStr">
+        <is>
+          <t>40 || 40</t>
+        </is>
+      </c>
+      <c r="BI123" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금 || out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:안함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:안함</t>
+        </is>
+      </c>
+      <c r="BJ123" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> || </t>
+        </is>
+      </c>
+      <c r="BK123" t="inlineStr"/>
+      <c r="BL123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM123" t="inlineStr"/>
+      <c r="BN123" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO123" t="inlineStr"/>
+      <c r="BP123" t="inlineStr"/>
+      <c r="BQ123" t="inlineStr"/>
+      <c r="BR123" t="inlineStr"/>
+      <c r="BS123" t="inlineStr"/>
+      <c r="BT123" t="inlineStr"/>
+      <c r="BU123" t="inlineStr"/>
+      <c r="BV123" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="BW123" t="inlineStr"/>
+      <c r="BX123" t="inlineStr"/>
+      <c r="BY123" t="inlineStr"/>
+      <c r="BZ123" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA123" t="inlineStr"/>
+      <c r="CB123" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC123" t="inlineStr">
+        <is>
+          <t>Se-75 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD123" t="inlineStr">
+        <is>
+          <t>조건없음 (1.0)</t>
+        </is>
+      </c>
+      <c r="CE123" t="inlineStr"/>
+      <c r="CF123" t="inlineStr"/>
+      <c r="CG123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM123" t="inlineStr"/>
+      <c r="CN123" t="inlineStr"/>
+      <c r="CO123" t="inlineStr"/>
+      <c r="CP123" t="inlineStr"/>
+      <c r="CQ123" t="inlineStr"/>
+      <c r="CR123" t="inlineStr"/>
+      <c r="CS123" t="inlineStr"/>
+      <c r="CT123" t="inlineStr"/>
+      <c r="CU123" t="inlineStr"/>
+      <c r="CV123" t="inlineStr"/>
+      <c r="CW123" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX123" t="inlineStr"/>
+      <c r="CY123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ123" t="inlineStr"/>
+      <c r="DA123" t="inlineStr">
+        <is>
+          <t>주배관</t>
+        </is>
+      </c>
+      <c r="DB123" t="inlineStr"/>
+      <c r="DC123" t="inlineStr"/>
+      <c r="DD123" t="inlineStr"/>
+      <c r="DE123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="n">
+        <v>30</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" s="1" t="n">
+        <v>46270.70486737975</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>4200</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>126000</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="V124" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~18:00</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr"/>
+      <c r="Y124" t="inlineStr"/>
+      <c r="Z124" t="inlineStr"/>
+      <c r="AA124" t="inlineStr"/>
+      <c r="AB124" t="inlineStr"/>
+      <c r="AC124" t="inlineStr"/>
+      <c r="AD124" t="inlineStr"/>
+      <c r="AE124" t="inlineStr"/>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="inlineStr"/>
+      <c r="AH124" t="inlineStr"/>
+      <c r="AI124" t="inlineStr"/>
+      <c r="AJ124" t="inlineStr"/>
+      <c r="AK124" t="inlineStr"/>
+      <c r="AL124" t="inlineStr"/>
+      <c r="AM124" t="inlineStr"/>
+      <c r="AN124" t="inlineStr"/>
+      <c r="AO124" t="inlineStr"/>
+      <c r="AP124" t="inlineStr"/>
+      <c r="AQ124" t="inlineStr"/>
+      <c r="AR124" t="inlineStr"/>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AU124" t="inlineStr"/>
+      <c r="AV124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr"/>
+      <c r="AX124" t="inlineStr"/>
+      <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG124" t="inlineStr">
+        <is>
+          <t>81루5100 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="BH124" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BI124" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:안함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:안함</t>
+        </is>
+      </c>
+      <c r="BJ124" t="inlineStr"/>
+      <c r="BK124" t="inlineStr"/>
+      <c r="BL124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM124" t="inlineStr"/>
+      <c r="BN124" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO124" t="inlineStr"/>
+      <c r="BP124" t="inlineStr"/>
+      <c r="BQ124" t="inlineStr"/>
+      <c r="BR124" t="inlineStr"/>
+      <c r="BS124" t="inlineStr"/>
+      <c r="BT124" t="inlineStr"/>
+      <c r="BU124" t="inlineStr"/>
+      <c r="BV124" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="BW124" t="inlineStr"/>
+      <c r="BX124" t="inlineStr"/>
+      <c r="BY124" t="inlineStr"/>
+      <c r="BZ124" t="inlineStr">
+        <is>
+          <t>I/D</t>
+        </is>
+      </c>
+      <c r="CA124" t="inlineStr"/>
+      <c r="CB124" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC124" t="inlineStr">
+        <is>
+          <t>250mm 초과 [10인치 이상] (1.0)</t>
+        </is>
+      </c>
+      <c r="CD124" t="inlineStr"/>
+      <c r="CE124" t="inlineStr"/>
+      <c r="CF124" t="inlineStr"/>
+      <c r="CG124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM124" t="inlineStr"/>
+      <c r="CN124" t="inlineStr"/>
+      <c r="CO124" t="inlineStr"/>
+      <c r="CP124" t="inlineStr"/>
+      <c r="CQ124" t="inlineStr"/>
+      <c r="CR124" t="inlineStr"/>
+      <c r="CS124" t="inlineStr"/>
+      <c r="CT124" t="inlineStr"/>
+      <c r="CU124" t="inlineStr"/>
+      <c r="CV124" t="inlineStr"/>
+      <c r="CW124" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX124" t="inlineStr"/>
+      <c r="CY124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ124" t="inlineStr"/>
+      <c r="DA124" t="inlineStr">
+        <is>
+          <t>주배관</t>
+        </is>
+      </c>
+      <c r="DB124" t="inlineStr"/>
+      <c r="DC124" t="inlineStr"/>
+      <c r="DD124" t="inlineStr"/>
+      <c r="DE124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>K1 PJT</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>410</v>
+      </c>
+      <c r="D125" t="n">
+        <v>48</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" s="1" t="n">
+        <v>46270.70677334409</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>과장 주영광</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>R-ray(se-75)</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>1224000</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>대리 우명광</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>주임 김진환</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>주임 김성렬</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>주임 이경재</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일06:00</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr"/>
+      <c r="AL125" t="inlineStr"/>
+      <c r="AM125" t="inlineStr"/>
+      <c r="AN125" t="inlineStr"/>
+      <c r="AO125" t="inlineStr"/>
+      <c r="AP125" t="inlineStr"/>
+      <c r="AQ125" t="inlineStr"/>
+      <c r="AR125" t="inlineStr"/>
+      <c r="AS125" t="inlineStr"/>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AU125" t="inlineStr"/>
+      <c r="AV125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr"/>
+      <c r="AX125" t="inlineStr"/>
+      <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG125" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스) || 90너4889 (탑차)</t>
+        </is>
+      </c>
+      <c r="BH125" t="inlineStr">
+        <is>
+          <t>40 || 40</t>
+        </is>
+      </c>
+      <c r="BI125" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금 || out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:안함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:안함</t>
+        </is>
+      </c>
+      <c r="BJ125" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> || </t>
+        </is>
+      </c>
+      <c r="BK125" t="inlineStr"/>
+      <c r="BL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM125" t="inlineStr"/>
+      <c r="BN125" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO125" t="inlineStr"/>
+      <c r="BP125" t="inlineStr"/>
+      <c r="BQ125" t="inlineStr"/>
+      <c r="BR125" t="inlineStr"/>
+      <c r="BS125" t="inlineStr"/>
+      <c r="BT125" t="inlineStr"/>
+      <c r="BU125" t="inlineStr"/>
+      <c r="BV125" t="inlineStr">
+        <is>
+          <t>pipe</t>
+        </is>
+      </c>
+      <c r="BW125" t="inlineStr"/>
+      <c r="BX125" t="inlineStr"/>
+      <c r="BY125" t="inlineStr"/>
+      <c r="BZ125" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA125" t="inlineStr"/>
+      <c r="CB125" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC125" t="inlineStr">
+        <is>
+          <t>Se-75 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD125" t="inlineStr">
+        <is>
+          <t>조건없음 (1.0)</t>
+        </is>
+      </c>
+      <c r="CE125" t="inlineStr"/>
+      <c r="CF125" t="inlineStr"/>
+      <c r="CG125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM125" t="inlineStr"/>
+      <c r="CN125" t="inlineStr"/>
+      <c r="CO125" t="inlineStr"/>
+      <c r="CP125" t="inlineStr"/>
+      <c r="CQ125" t="inlineStr"/>
+      <c r="CR125" t="inlineStr"/>
+      <c r="CS125" t="inlineStr"/>
+      <c r="CT125" t="inlineStr"/>
+      <c r="CU125" t="inlineStr"/>
+      <c r="CV125" t="inlineStr"/>
+      <c r="CW125" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX125" t="inlineStr"/>
+      <c r="CY125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ125" t="inlineStr"/>
+      <c r="DA125" t="inlineStr">
+        <is>
+          <t>주배관</t>
+        </is>
+      </c>
+      <c r="DB125" t="inlineStr"/>
+      <c r="DC125" t="inlineStr"/>
+      <c r="DD125" t="inlineStr"/>
+      <c r="DE125" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/home/data/Lotte_Material_Inventory.xlsx
+++ b/home/data/Lotte_Material_Inventory.xlsx
@@ -21,11 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -56,10 +54,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -30233,7 +30230,7 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>45992.69273418081</v>
+        <v>45992.69273417824</v>
       </c>
       <c r="B95" t="n">
         <v>420</v>
@@ -30280,7 +30277,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>45992.69273418081</v>
+        <v>45992.69273417824</v>
       </c>
       <c r="B96" t="n">
         <v>418</v>
@@ -30355,10 +30352,26 @@
           <t>K1 PJT</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
@@ -30402,10 +30415,26 @@
           <t>K1 PJT</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
@@ -30421,7 +30450,7 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>45993.69565744384</v>
+        <v>45993.69565744213</v>
       </c>
       <c r="B99" t="n">
         <v>420</v>
@@ -30468,7 +30497,7 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>45999.69990378177</v>
+        <v>45999.69990378472</v>
       </c>
       <c r="B100" t="n">
         <v>420</v>
@@ -30543,10 +30572,26 @@
           <t>K1 PJT</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
@@ -30590,10 +30635,26 @@
           <t>K1 PJT</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
@@ -30637,10 +30698,26 @@
           <t>K1 PJT</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
@@ -30684,10 +30761,26 @@
           <t>K1 PJT</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
@@ -30731,10 +30824,26 @@
           <t>K1 PJT</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
@@ -30778,10 +30887,26 @@
           <t>K1 PJT</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스) || 90너4889 (탑차)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>40 || 40</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금 || out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:안함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:안함</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>||</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
@@ -30825,10 +30950,26 @@
           <t>K1 PJT</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스) || 90너4889 (탑차)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>40 || 40</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금 || out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:안함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:안함</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>||</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
@@ -30844,7 +30985,7 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46002.70486741902</v>
+        <v>46002.70486741898</v>
       </c>
       <c r="B108" t="n">
         <v>420</v>
@@ -30891,7 +31032,7 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46002.70486741902</v>
+        <v>46002.70486741898</v>
       </c>
       <c r="B109" t="n">
         <v>418</v>
@@ -30966,10 +31107,26 @@
           <t>K1 PJT</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스) || 90너4889 (탑차)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>40 || 40</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금 || out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:안함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:안함</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>||</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
@@ -60894,7 +61051,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -60908,7 +61065,7 @@
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" s="1" t="n">
-        <v>46270.6927341525</v>
+        <v>46270.69273415509</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -61112,10 +61269,8 @@
         </is>
       </c>
       <c r="CX112" t="inlineStr"/>
-      <c r="CY112" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="CY112" t="n">
+        <v>0</v>
       </c>
       <c r="CZ112" t="inlineStr"/>
       <c r="DA112" t="inlineStr">
@@ -61126,10 +61281,12 @@
       <c r="DB112" t="inlineStr"/>
       <c r="DC112" t="inlineStr"/>
       <c r="DD112" t="inlineStr"/>
-      <c r="DE112" t="inlineStr"/>
+      <c r="DE112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -61145,7 +61302,7 @@
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" s="1" t="n">
-        <v>46270.69409599712</v>
+        <v>46270.69409599537</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -61389,10 +61546,8 @@
         </is>
       </c>
       <c r="CX113" t="inlineStr"/>
-      <c r="CY113" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="CY113" t="n">
+        <v>0</v>
       </c>
       <c r="CZ113" t="inlineStr"/>
       <c r="DA113" t="inlineStr">
@@ -61403,10 +61558,12 @@
       <c r="DB113" t="inlineStr"/>
       <c r="DC113" t="inlineStr"/>
       <c r="DD113" t="inlineStr"/>
-      <c r="DE113" t="inlineStr"/>
+      <c r="DE113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>45993</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -61422,7 +61579,7 @@
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" s="1" t="n">
-        <v>46270.69484850537</v>
+        <v>46270.69484850694</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -61666,10 +61823,8 @@
         </is>
       </c>
       <c r="CX114" t="inlineStr"/>
-      <c r="CY114" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="CY114" t="n">
+        <v>0</v>
       </c>
       <c r="CZ114" t="inlineStr"/>
       <c r="DA114" t="inlineStr">
@@ -61680,10 +61835,12 @@
       <c r="DB114" t="inlineStr"/>
       <c r="DC114" t="inlineStr"/>
       <c r="DD114" t="inlineStr"/>
-      <c r="DE114" t="inlineStr"/>
+      <c r="DE114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>45993</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -61697,7 +61854,7 @@
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" s="1" t="n">
-        <v>46270.6956574165</v>
+        <v>46270.69565741898</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -61901,10 +62058,8 @@
         </is>
       </c>
       <c r="CX115" t="inlineStr"/>
-      <c r="CY115" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="CY115" t="n">
+        <v>0</v>
       </c>
       <c r="CZ115" t="inlineStr"/>
       <c r="DA115" t="inlineStr">
@@ -61915,10 +62070,12 @@
       <c r="DB115" t="inlineStr"/>
       <c r="DC115" t="inlineStr"/>
       <c r="DD115" t="inlineStr"/>
-      <c r="DE115" t="inlineStr"/>
+      <c r="DE115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>45999</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -61932,7 +62089,7 @@
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" s="1" t="n">
-        <v>46270.69990375041</v>
+        <v>46270.69990375</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -62136,10 +62293,8 @@
         </is>
       </c>
       <c r="CX116" t="inlineStr"/>
-      <c r="CY116" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="CY116" t="n">
+        <v>0</v>
       </c>
       <c r="CZ116" t="inlineStr"/>
       <c r="DA116" t="inlineStr">
@@ -62150,10 +62305,12 @@
       <c r="DB116" t="inlineStr"/>
       <c r="DC116" t="inlineStr"/>
       <c r="DD116" t="inlineStr"/>
-      <c r="DE116" t="inlineStr"/>
+      <c r="DE116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>45999</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -62169,7 +62326,7 @@
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" s="1" t="n">
-        <v>46270.70089576427</v>
+        <v>46270.70089576389</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -62429,10 +62586,8 @@
         </is>
       </c>
       <c r="CX117" t="inlineStr"/>
-      <c r="CY117" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="CY117" t="n">
+        <v>0</v>
       </c>
       <c r="CZ117" t="inlineStr"/>
       <c r="DA117" t="inlineStr">
@@ -62443,10 +62598,12 @@
       <c r="DB117" t="inlineStr"/>
       <c r="DC117" t="inlineStr"/>
       <c r="DD117" t="inlineStr"/>
-      <c r="DE117" t="inlineStr"/>
+      <c r="DE117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>45996</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -62462,7 +62619,7 @@
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" s="1" t="n">
-        <v>46270.70108447342</v>
+        <v>46270.70108447917</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -62718,10 +62875,8 @@
         </is>
       </c>
       <c r="CX118" t="inlineStr"/>
-      <c r="CY118" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="CY118" t="n">
+        <v>0</v>
       </c>
       <c r="CZ118" t="inlineStr"/>
       <c r="DA118" t="inlineStr">
@@ -62732,10 +62887,12 @@
       <c r="DB118" t="inlineStr"/>
       <c r="DC118" t="inlineStr"/>
       <c r="DD118" t="inlineStr"/>
-      <c r="DE118" t="inlineStr"/>
+      <c r="DE118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>45994</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -62751,7 +62908,7 @@
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" s="1" t="n">
-        <v>46270.70124387546</v>
+        <v>46270.70124387732</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -62995,10 +63152,8 @@
         </is>
       </c>
       <c r="CX119" t="inlineStr"/>
-      <c r="CY119" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="CY119" t="n">
+        <v>0</v>
       </c>
       <c r="CZ119" t="inlineStr"/>
       <c r="DA119" t="inlineStr">
@@ -63009,10 +63164,12 @@
       <c r="DB119" t="inlineStr"/>
       <c r="DC119" t="inlineStr"/>
       <c r="DD119" t="inlineStr"/>
-      <c r="DE119" t="inlineStr"/>
+      <c r="DE119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>45995</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -63028,7 +63185,7 @@
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" s="1" t="n">
-        <v>46270.7014567442</v>
+        <v>46270.70145674769</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -63284,10 +63441,8 @@
         </is>
       </c>
       <c r="CX120" t="inlineStr"/>
-      <c r="CY120" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="CY120" t="n">
+        <v>0</v>
       </c>
       <c r="CZ120" t="inlineStr"/>
       <c r="DA120" t="inlineStr">
@@ -63298,10 +63453,12 @@
       <c r="DB120" t="inlineStr"/>
       <c r="DC120" t="inlineStr"/>
       <c r="DD120" t="inlineStr"/>
-      <c r="DE120" t="inlineStr"/>
+      <c r="DE120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>46000</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -63317,7 +63474,7 @@
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" s="1" t="n">
-        <v>46270.70231902078</v>
+        <v>46270.70231901621</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -63577,10 +63734,8 @@
         </is>
       </c>
       <c r="CX121" t="inlineStr"/>
-      <c r="CY121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="CY121" t="n">
+        <v>0</v>
       </c>
       <c r="CZ121" t="inlineStr"/>
       <c r="DA121" t="inlineStr">
@@ -63591,10 +63746,12 @@
       <c r="DB121" t="inlineStr"/>
       <c r="DC121" t="inlineStr"/>
       <c r="DD121" t="inlineStr"/>
-      <c r="DE121" t="inlineStr"/>
+      <c r="DE121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>46001</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -63610,7 +63767,7 @@
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" s="1" t="n">
-        <v>46270.7032602737</v>
+        <v>46270.70326027778</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -63789,7 +63946,7 @@
       </c>
       <c r="BJ122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> || </t>
+          <t>||</t>
         </is>
       </c>
       <c r="BK122" t="inlineStr"/>
@@ -63874,10 +64031,8 @@
         </is>
       </c>
       <c r="CX122" t="inlineStr"/>
-      <c r="CY122" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="CY122" t="n">
+        <v>0</v>
       </c>
       <c r="CZ122" t="inlineStr"/>
       <c r="DA122" t="inlineStr">
@@ -63888,10 +64043,12 @@
       <c r="DB122" t="inlineStr"/>
       <c r="DC122" t="inlineStr"/>
       <c r="DD122" t="inlineStr"/>
-      <c r="DE122" t="inlineStr"/>
+      <c r="DE122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>46002</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -63907,7 +64064,7 @@
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" s="1" t="n">
-        <v>46270.70438769966</v>
+        <v>46270.70438769676</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -64094,7 +64251,7 @@
       </c>
       <c r="BJ123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> || </t>
+          <t>||</t>
         </is>
       </c>
       <c r="BK123" t="inlineStr"/>
@@ -64179,10 +64336,8 @@
         </is>
       </c>
       <c r="CX123" t="inlineStr"/>
-      <c r="CY123" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="CY123" t="n">
+        <v>0</v>
       </c>
       <c r="CZ123" t="inlineStr"/>
       <c r="DA123" t="inlineStr">
@@ -64193,10 +64348,12 @@
       <c r="DB123" t="inlineStr"/>
       <c r="DC123" t="inlineStr"/>
       <c r="DD123" t="inlineStr"/>
-      <c r="DE123" t="inlineStr"/>
+      <c r="DE123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>46002</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -64210,7 +64367,7 @@
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" s="1" t="n">
-        <v>46270.70486737975</v>
+        <v>46270.70486738426</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -64410,10 +64567,8 @@
         </is>
       </c>
       <c r="CX124" t="inlineStr"/>
-      <c r="CY124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="CY124" t="n">
+        <v>0</v>
       </c>
       <c r="CZ124" t="inlineStr"/>
       <c r="DA124" t="inlineStr">
@@ -64424,10 +64579,12 @@
       <c r="DB124" t="inlineStr"/>
       <c r="DC124" t="inlineStr"/>
       <c r="DD124" t="inlineStr"/>
-      <c r="DE124" t="inlineStr"/>
+      <c r="DE124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>46006</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -64443,7 +64600,7 @@
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" s="1" t="n">
-        <v>46270.70677334409</v>
+        <v>46270.70677334491</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -64622,7 +64779,7 @@
       </c>
       <c r="BJ125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> || </t>
+          <t>||</t>
         </is>
       </c>
       <c r="BK125" t="inlineStr"/>
@@ -64707,10 +64864,8 @@
         </is>
       </c>
       <c r="CX125" t="inlineStr"/>
-      <c r="CY125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="CY125" t="n">
+        <v>0</v>
       </c>
       <c r="CZ125" t="inlineStr"/>
       <c r="DA125" t="inlineStr">
@@ -64721,7 +64876,9 @@
       <c r="DB125" t="inlineStr"/>
       <c r="DC125" t="inlineStr"/>
       <c r="DD125" t="inlineStr"/>
-      <c r="DE125" t="inlineStr"/>
+      <c r="DE125" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
